--- a/public/template.xlsx
+++ b/public/template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\optik-master\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8830BAE8-CB8E-4900-A53F-EF08140C859F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{211E5467-9D14-4A69-A42F-A9C900E0DDB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E365AF81-CDDA-4854-81BD-2694F7C96748}"/>
+    <workbookView xWindow="4908" yWindow="5172" windowWidth="16896" windowHeight="7776" xr2:uid="{E365AF81-CDDA-4854-81BD-2694F7C96748}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Nama</t>
   </si>
@@ -76,6 +76,12 @@
   </si>
   <si>
     <t>diabetes</t>
+  </si>
+  <si>
+    <t>no_bpjs</t>
+  </si>
+  <si>
+    <t>32483849207</t>
   </si>
 </sst>
 </file>
@@ -439,14 +445,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E821402A-0147-4712-BACD-BAD2E8928D49}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="8.88671875" style="1"/>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -460,16 +466,19 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -482,19 +491,22 @@
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{9E52CE6D-1DEE-4CFC-8AB4-6D48707D0079}"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{9E52CE6D-1DEE-4CFC-8AB4-6D48707D0079}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
